--- a/Scripts/layouts/oferta_academicav2.2.xlsx
+++ b/Scripts/layouts/oferta_academicav2.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Documents\METODOLOGIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Documents\Athena\Scripts\layouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D09C9890-C60A-42D3-8A2B-94C6D6FC0876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671EB9B-E089-44DC-936C-E02519FD0ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3345" yWindow="1695" windowWidth="21810" windowHeight="11910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="area" sheetId="4" r:id="rId1"/>
@@ -1960,15 +1960,9 @@
     <t>Preservación de la riqueza natural, cultural y patrimonio histórico con visión sustentable</t>
   </si>
   <si>
-    <t>id_area</t>
-  </si>
-  <si>
     <t>nombre_area</t>
   </si>
   <si>
-    <t>id_escuela</t>
-  </si>
-  <si>
     <t>nombre_escuela</t>
   </si>
   <si>
@@ -2057,6 +2051,12 @@
   </si>
   <si>
     <t>id_carrera</t>
+  </si>
+  <si>
+    <t>area_id</t>
+  </si>
+  <si>
+    <t>escuela_id</t>
   </si>
 </sst>
 </file>
@@ -2197,7 +2197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2250,12 +2250,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2567,10 +2561,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>643</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2613,10 +2607,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2624,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2632,7 +2626,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2640,7 +2634,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2648,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2656,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2664,7 +2658,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2672,7 +2666,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2680,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2688,7 +2682,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2696,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2704,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2712,7 +2706,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2720,7 +2714,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2728,7 +2722,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2736,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2744,7 +2738,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2752,7 +2746,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2760,7 +2754,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2768,7 +2762,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2776,7 +2770,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2784,7 +2778,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2792,7 +2786,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2800,7 +2794,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2808,7 +2802,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2816,7 +2810,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2824,7 +2818,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -2853,17 +2847,17 @@
         <v>1</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>643</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2874,18 +2868,18 @@
       <c r="B3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2896,18 +2890,18 @@
       <c r="B5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2918,18 +2912,18 @@
       <c r="B7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2940,18 +2934,18 @@
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2962,18 +2956,18 @@
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2984,18 +2978,18 @@
       <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3006,18 +3000,18 @@
       <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3028,18 +3022,18 @@
       <c r="B17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3050,18 +3044,18 @@
       <c r="B19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3072,18 +3066,18 @@
       <c r="B21" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3094,18 +3088,18 @@
       <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3116,18 +3110,18 @@
       <c r="B25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3138,18 +3132,18 @@
       <c r="B27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3160,18 +3154,18 @@
       <c r="B29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3182,18 +3176,18 @@
       <c r="B31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3204,18 +3198,18 @@
       <c r="B33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3226,18 +3220,18 @@
       <c r="B35" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3248,12 +3242,12 @@
       <c r="B37" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -3275,7 +3269,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -3297,7 +3291,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -3314,18 +3308,18 @@
       <c r="B43" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3341,7 +3335,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="19">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -3363,7 +3357,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="19">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -3385,7 +3379,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -3407,7 +3401,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
@@ -3429,7 +3423,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="19">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -3451,7 +3445,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
@@ -3473,7 +3467,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -3495,7 +3489,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
@@ -3517,7 +3511,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -3539,7 +3533,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="19">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -3561,7 +3555,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="19">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -3603,10 +3597,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5650,10 +5644,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/Scripts/layouts/oferta_academicav2.2.xlsx
+++ b/Scripts/layouts/oferta_academicav2.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Documents\Athena\Scripts\layouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671EB9B-E089-44DC-936C-E02519FD0ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C75095C-9536-4F89-869A-EBD8D5BD49C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Scripts/layouts/oferta_academicav2.2.xlsx
+++ b/Scripts/layouts/oferta_academicav2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Documents\Athena\Scripts\layouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C75095C-9536-4F89-869A-EBD8D5BD49C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C8AE20-C1AE-4B42-A126-FC114D303F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="area" sheetId="4" r:id="rId1"/>

--- a/Scripts/layouts/oferta_academicav2.2.xlsx
+++ b/Scripts/layouts/oferta_academicav2.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Documents\Athena\Scripts\layouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C8AE20-C1AE-4B42-A126-FC114D303F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C64CC042-DC97-4156-90CF-B0444FF060A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2105,7 +2105,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2154,6 +2154,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -2197,7 +2203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2249,6 +2255,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2843,7 +2852,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="18" t="s">
